--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-observation-groupe-questionnaires-evaluation.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-observation-groupe-questionnaires-evaluation.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>FR - Groupe de questionnaires d'évaluation</t>
+    <t>Observation - Fr Groupe de questionnaires d'évaluation</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-observation-groupe-questionnaires-evaluation.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-observation-groupe-questionnaires-evaluation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
